--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44385-2025 artfynd.xlsx
+++ b/artfynd/A 44385-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130684443</v>
       </c>
       <c r="B2" t="n">
-        <v>101215</v>
+        <v>101325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130684446</v>
       </c>
       <c r="B3" t="n">
-        <v>101215</v>
+        <v>101325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130684449</v>
       </c>
       <c r="B4" t="n">
-        <v>101215</v>
+        <v>101325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
